--- a/Result/profitability/4105.xlsx
+++ b/Result/profitability/4105.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.76</v>
       </c>
       <c r="M2" t="n">
-        <v>1.55625</v>
+        <v>1.5725</v>
       </c>
       <c r="N2" t="n">
-        <v>58.15750000000001</v>
+        <v>57.74375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4625</v>
+        <v>1.3975</v>
       </c>
       <c r="N3" t="n">
-        <v>58.24625</v>
+        <v>59.13875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1.28125</v>
+        <v>1.28875</v>
       </c>
       <c r="N4" t="n">
-        <v>58.6525</v>
+        <v>58.4125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>1.16</v>
+        <v>1.22125</v>
       </c>
       <c r="N5" t="n">
-        <v>60.09125</v>
+        <v>60.09375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>1.085</v>
+        <v>0.9974999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>60.065</v>
+        <v>60.45375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.91875</v>
+        <v>0.97</v>
       </c>
       <c r="N7" t="n">
-        <v>61.01625</v>
+        <v>61.31</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8525</v>
+        <v>0.83375</v>
       </c>
       <c r="N8" t="n">
-        <v>61.5875</v>
+        <v>61.4275</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.68625</v>
       </c>
       <c r="N9" t="n">
-        <v>61.865</v>
+        <v>61.86499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0.75</v>
       </c>
       <c r="N11" t="n">
-        <v>62.95875</v>
+        <v>62.95874999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.51</v>
       </c>
       <c r="M12" t="n">
-        <v>0.72625</v>
+        <v>0.7262500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>63.7775</v>
@@ -2026,10 +2026,10 @@
         <v>0.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6825</v>
+        <v>0.6825000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>62.885</v>
+        <v>62.88500000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1652</v>
+      </c>
+      <c r="D75" t="n">
+        <v>682</v>
+      </c>
+      <c r="E75" t="n">
+        <v>970</v>
+      </c>
+      <c r="F75" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>487</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>29.49%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>57</v>
+      </c>
+      <c r="J75" t="n">
+        <v>544</v>
+      </c>
+      <c r="K75" t="n">
+        <v>406</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="N75" t="n">
+        <v>57.94625000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.1500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.08426966292134841</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.280000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0213368894815803</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4298245614035088</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.02000000000000313</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.0003407735559721736</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
